--- a/test_codes/百度表格-简化层级版.xlsx
+++ b/test_codes/百度表格-简化层级版.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Table1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Table1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -419,7 +419,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G17"/>
+  <dimension ref="A1:G24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -433,627 +433,718 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr"/>
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>(人民币百万元，百分比除外)</t>
+        </is>
+      </c>
       <c r="B1" s="2" t="inlineStr">
         <is>
-          <t>2024年12月31日</t>
+          <t>平均余额</t>
         </is>
       </c>
       <c r="C1" s="2" t="inlineStr">
         <is>
-          <t>2024年12月31日</t>
+          <t>利息收入
+支出</t>
         </is>
       </c>
       <c r="D1" s="2" t="inlineStr">
         <is>
-          <t>2023年12月31日</t>
+          <t>平均收益率
+成本率(%)</t>
         </is>
       </c>
       <c r="E1" s="2" t="inlineStr">
         <is>
-          <t>2023年12月31日</t>
+          <t>平均余额</t>
         </is>
       </c>
       <c r="F1" s="2" t="inlineStr">
         <is>
-          <t>2022年12月31日</t>
+          <t>利息收入
+支出</t>
         </is>
       </c>
       <c r="G1" s="2" t="inlineStr">
         <is>
-          <t>2022年12月31日</t>
+          <t>平均收益率/
+成本率(%)</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>(人民币百万元，百分比除外)</t>
-        </is>
-      </c>
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t>金额</t>
-        </is>
-      </c>
-      <c r="C2" s="2" t="inlineStr">
-        <is>
-          <t>占比(%)</t>
-        </is>
-      </c>
-      <c r="D2" s="2" t="inlineStr">
-        <is>
-          <t>金额</t>
-        </is>
-      </c>
-      <c r="E2" s="2" t="inlineStr">
-        <is>
-          <t>占比(%)</t>
-        </is>
-      </c>
-      <c r="F2" s="2" t="inlineStr">
-        <is>
-          <t>金额</t>
-        </is>
-      </c>
-      <c r="G2" s="2" t="inlineStr">
-        <is>
-          <t>占比(%)</t>
-        </is>
-      </c>
+          <t>资产</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr"/>
+      <c r="C2" s="2" t="inlineStr"/>
+      <c r="D2" s="2" t="inlineStr"/>
+      <c r="E2" s="2" t="inlineStr"/>
+      <c r="F2" s="2" t="inlineStr"/>
+      <c r="G2" s="2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>本行境内贷款和垫款</t>
+          <t>发放贷款和垫款总额</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>24,938,748</t>
+          <t>25,228,241</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>96.50</t>
+          <t>864,902</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>23,006,496</t>
+          <t>3.43</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>96.42</t>
+          <t>22,996,225</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>20,305,569</t>
+          <t>877,917</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>95.80</t>
+          <t>3.82</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>公司类贷款和垫款</t>
+          <t>金融投资</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>14,434,401</t>
+          <t>9,363,532</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>55.86</t>
+          <t>289,788</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>13,225,655</t>
+          <t>3.09</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>55.43</t>
+          <t>8,576,102</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>11,020,150</t>
+          <t>278,524</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>51.99</t>
+          <t>3.25</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>短期贷款</t>
+          <t>存放中央银行款项</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>4,014,375</t>
+          <t>2,680,183</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>15.54</t>
+          <t>44,878</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>3,594,305</t>
+          <t>1.67</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>15.06</t>
+          <t>2,741,943</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>2,927,713</t>
+          <t>45,636</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>13.81</t>
+          <t>1.66</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>中长期贷款</t>
+          <t>存放同业款项及拆出资金</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>10,420,026</t>
+          <t>885,333</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>40.32</t>
+          <t>25,228</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>9,631,350</t>
+          <t>2.85</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>40.37</t>
+          <t>862,984</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>8,092,437</t>
+          <t>25,678</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>38.18</t>
+          <t>2.98</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>个人贷款和垫款</t>
+          <t>买入返售金融资产</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>8,872,595</t>
+          <t>943,008</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>34.33</t>
+          <t>16,761</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>8,676,054</t>
+          <t>1.78</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>36.36</t>
+          <t>1,027,075</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>8,236,768</t>
+          <t>19,611</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>38.86</t>
+          <t>1.91</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>个人住房贷款</t>
+          <t>总生息资产</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>6,187,858</t>
+          <t>39,100,297</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>23.94</t>
+          <t>1,241,557</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>6,386,525</t>
+          <t>3.18</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>26.76</t>
+          <t>36,204,329</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>6,479,609</t>
+          <t>1,247,366</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>30.57</t>
+          <t>3.45</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>信用卡贷款</t>
+          <t>总减值准备</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>1,065,883</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>4.13</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>997,133</t>
-        </is>
-      </c>
+          <t>(823,273)</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr"/>
+      <c r="D9" s="2" t="inlineStr"/>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>4.18</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>924,873</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>4.37</t>
-        </is>
-      </c>
+          <t>(780,649)</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr"/>
+      <c r="G9" s="2" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>个人经营贷款</t>
+          <t>非生息资产</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>1,021,693</t>
-        </is>
-      </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>3.95</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>777,481</t>
-        </is>
-      </c>
+          <t>1,903,318</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr"/>
+      <c r="D10" s="2" t="inlineStr"/>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>3.26</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>415,344</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>1.96</t>
-        </is>
-      </c>
+          <t>1,770,148</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr"/>
+      <c r="G10" s="2" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>个人消费贷款</t>
+          <t>资产总额</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>527,895</t>
+          <t>40,180,342</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>2.04</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>421,623</t>
-        </is>
-      </c>
+          <t>1,241,557</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr"/>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>1.77</t>
+          <t>37,193,828</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>295,443</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>1.39</t>
-        </is>
-      </c>
+          <t>1,247,366</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>其他贷款</t>
-        </is>
-      </c>
-      <c r="B12" s="2" t="inlineStr">
-        <is>
-          <t>69,266</t>
-        </is>
-      </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>0.27</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>93,292</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>0.39</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>121,499</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>0.57</t>
-        </is>
-      </c>
+          <t>负债</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr"/>
+      <c r="C12" s="2" t="inlineStr"/>
+      <c r="D12" s="2" t="inlineStr"/>
+      <c r="E12" s="2" t="inlineStr"/>
+      <c r="F12" s="2" t="inlineStr"/>
+      <c r="G12" s="2" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>票据贴现</t>
+          <t>吸收存款</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>1,631,752</t>
+          <t>27,836,873</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>6.31</t>
+          <t>458,828</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>1,104,787</t>
+          <t>1.65</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>4.63</t>
+          <t>26,453,554</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>1,048,651</t>
+          <t>468,003</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>4.95</t>
+          <t>1.77</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>境外和子公司</t>
+          <t>同业及其他金融机构存放款项和拆入资金</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>854,969</t>
+          <t>4,025,481</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>3.31</t>
+          <t>97,731</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>804,486</t>
+          <t>2.43</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>3.37</t>
+          <t>3,238,337</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>842,566</t>
+          <t>80,879</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>3.97</t>
+          <t>2.50</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>应计利息</t>
+          <t>已发行债务证券</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>49,577</t>
+          <t>2,046,824</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0.19</t>
+          <t>63,860</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>50,618</t>
+          <t>3.12</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0.21</t>
+          <t>1,727,343</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>48,995</t>
+          <t>54,504</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0.23</t>
+          <t>3.16</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>发放贷款和垫款总额</t>
+          <t>向中央银行借款</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>25,843,294</t>
+          <t>1,071,408</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>100.00</t>
+          <t>27,137</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>23,861,600</t>
+          <t>2.53</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>100.00</t>
+          <t>887,112</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>21,197,130</t>
+          <t>23,785</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>100.00</t>
+          <t>2.68</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>发放贷款和垫款总额</t>
+          <t>卖出回购金融资产款</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>25,843,294</t>
+          <t>183,449</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>100.00</t>
+          <t>4,119</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>23,861,600</t>
+          <t>2.25</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>100.00</t>
+          <t>88,095</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>21,197,130</t>
+          <t>2,962</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>100.00</t>
+          <t>3.36</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="inlineStr">
+        <is>
+          <t>总计息负债</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>35,164,035</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>651,675</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>1.85</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>32,394,441</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>630,133</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>1.95</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>非计息负债</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>1,710,813</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr"/>
+      <c r="D19" s="2" t="inlineStr"/>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>1,785,647</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr"/>
+      <c r="G19" s="2" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="inlineStr">
+        <is>
+          <t>负债总额</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>36,874,848</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>651,675</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr"/>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>34,180,088</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>630,133</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="inlineStr">
+        <is>
+          <t>利息净收入</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr"/>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>589,882</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr"/>
+      <c r="E21" s="2" t="inlineStr"/>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>617,233</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="inlineStr">
+        <is>
+          <t>净利差</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr"/>
+      <c r="C22" s="2" t="inlineStr"/>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>1.33</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr"/>
+      <c r="F22" s="2" t="inlineStr"/>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>1.50</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="inlineStr">
+        <is>
+          <t>净利息收益率</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr"/>
+      <c r="C23" s="2" t="inlineStr"/>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>1.51</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr"/>
+      <c r="F23" s="2" t="inlineStr"/>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>1.70</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="inlineStr">
+        <is>
+          <t>净利息收益率</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr"/>
+      <c r="C24" s="2" t="inlineStr"/>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>1.51</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr"/>
+      <c r="F24" s="2" t="inlineStr"/>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>1.70</t>
         </is>
       </c>
     </row>
